--- a/data/gdpbenelux.xlsx
+++ b/data/gdpbenelux.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luukn\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luukn\Documents\GitHub\happiness\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CC06303-DA11-4439-8B95-C2A442E2D0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246E72D0-31AA-449E-9B51-D2643B7266C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{5CB4922B-3EE8-4B65-880B-50B1B55D9DF3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Belgium</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>1,227,544</t>
+  </si>
+  <si>
+    <t>Country</t>
   </si>
 </sst>
 </file>
@@ -448,6 +451,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="B1">
         <v>2014</v>
       </c>
@@ -614,6 +620,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D25CF0B9B9713944843C6634AD94B5CD" ma:contentTypeVersion="4" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="6fc06c35c9fb9ff8495a9005fb1aa923">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f4a0f2c8-0374-43bc-b7f6-d31395797ed2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ffa17790aa560c96c4a002fed6eed5a2" ns3:_="">
     <xsd:import namespace="f4a0f2c8-0374-43bc-b7f6-d31395797ed2"/>
@@ -757,15 +772,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -773,6 +779,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9BA2348-B4A9-433B-8E09-86B1A484E3C9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C64B52EA-6A09-4710-A973-6D7843483BB8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -790,14 +804,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9BA2348-B4A9-433B-8E09-86B1A484E3C9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADEAF920-3273-4C85-B8A9-2A3E9F7C5CAA}">
   <ds:schemaRefs/>

--- a/data/gdpbenelux.xlsx
+++ b/data/gdpbenelux.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luukn\Documents\GitHub\happiness\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246E72D0-31AA-449E-9B51-D2643B7266C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78DDAEE-080F-4227-B066-A0610E53D592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{5CB4922B-3EE8-4B65-880B-50B1B55D9DF3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Belgium</t>
   </si>
@@ -45,21 +45,6 @@
   </si>
   <si>
     <t>Luxembourg</t>
-  </si>
-  <si>
-    <t>1,320,635</t>
-  </si>
-  <si>
-    <t>1,054,472</t>
-  </si>
-  <si>
-    <t>1,046,541</t>
-  </si>
-  <si>
-    <t>1,154,361</t>
-  </si>
-  <si>
-    <t>1,227,544</t>
   </si>
   <si>
     <t>Country</t>
@@ -106,9 +91,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,7 +438,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B1">
         <v>2014</v>
@@ -557,20 +543,20 @@
       <c r="H3">
         <v>923.56100000000004</v>
       </c>
-      <c r="I3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" t="s">
-        <v>7</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3</v>
+      <c r="I3" s="2">
+        <v>1054.472</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1046.5409999999999</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1154.3610000000001</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1227.5440000000001</v>
+      </c>
+      <c r="M3" s="2">
+        <v>1320.635</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -620,15 +606,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D25CF0B9B9713944843C6634AD94B5CD" ma:contentTypeVersion="4" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="6fc06c35c9fb9ff8495a9005fb1aa923">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f4a0f2c8-0374-43bc-b7f6-d31395797ed2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ffa17790aa560c96c4a002fed6eed5a2" ns3:_="">
     <xsd:import namespace="f4a0f2c8-0374-43bc-b7f6-d31395797ed2"/>
@@ -772,6 +749,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -779,14 +765,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9BA2348-B4A9-433B-8E09-86B1A484E3C9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C64B52EA-6A09-4710-A973-6D7843483BB8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -804,6 +782,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9BA2348-B4A9-433B-8E09-86B1A484E3C9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADEAF920-3273-4C85-B8A9-2A3E9F7C5CAA}">
   <ds:schemaRefs/>

--- a/data/gdpbenelux.xlsx
+++ b/data/gdpbenelux.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luukn\Documents\GitHub\happiness\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78DDAEE-080F-4227-B066-A0610E53D592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD488A3-DFC2-4CCF-8804-ED3D3A8A3C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{5CB4922B-3EE8-4B65-880B-50B1B55D9DF3}"/>
   </bookViews>
@@ -54,6 +54,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -91,10 +94,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -482,81 +486,81 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>537.98699999999997</v>
+        <v>111.2</v>
       </c>
       <c r="C2">
-        <v>461.04500000000002</v>
+        <v>111.2</v>
       </c>
       <c r="D2">
-        <v>474.27199999999999</v>
+        <v>113.3</v>
       </c>
       <c r="E2">
-        <v>500.90899999999999</v>
+        <v>114.3</v>
       </c>
       <c r="F2">
-        <v>542.63900000000001</v>
+        <v>114.7</v>
       </c>
       <c r="G2">
-        <v>536.726</v>
+        <v>114.9</v>
       </c>
       <c r="H2">
-        <v>529.69399999999996</v>
+        <v>113.6</v>
       </c>
       <c r="I2">
-        <v>598.52200000000005</v>
+        <v>115.5</v>
       </c>
       <c r="J2">
-        <v>593.61500000000001</v>
+        <v>117.4</v>
       </c>
       <c r="K2">
-        <v>644.65499999999997</v>
+        <v>116.9</v>
       </c>
       <c r="L2">
-        <v>664.56399999999996</v>
+        <v>116.7</v>
       </c>
       <c r="M2">
-        <v>716.98</v>
+        <v>116.2</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>901.55700000000002</v>
-      </c>
-      <c r="C3">
-        <v>775.74400000000003</v>
-      </c>
-      <c r="D3">
-        <v>797.16399999999999</v>
-      </c>
-      <c r="E3">
-        <v>848.23400000000004</v>
-      </c>
-      <c r="F3">
-        <v>929.73400000000004</v>
-      </c>
-      <c r="G3">
-        <v>928.90300000000002</v>
-      </c>
-      <c r="H3">
-        <v>923.56100000000004</v>
+      <c r="B3" s="3">
+        <v>114</v>
+      </c>
+      <c r="C3" s="2">
+        <v>114.1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>115.8</v>
+      </c>
+      <c r="E3" s="2">
+        <v>114.8</v>
+      </c>
+      <c r="F3" s="2">
+        <v>114.3</v>
+      </c>
+      <c r="G3" s="2">
+        <v>117.1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>116.2</v>
       </c>
       <c r="I3" s="2">
-        <v>1054.472</v>
+        <v>108.5</v>
       </c>
       <c r="J3" s="2">
-        <v>1046.5409999999999</v>
+        <v>107.9</v>
       </c>
       <c r="K3" s="2">
-        <v>1154.3610000000001</v>
+        <v>115.6</v>
       </c>
       <c r="L3" s="2">
-        <v>1227.5440000000001</v>
+        <v>115.1</v>
       </c>
       <c r="M3" s="2">
-        <v>1320.635</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -564,40 +568,40 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>68.805000000000007</v>
+        <v>125.8</v>
       </c>
       <c r="C4">
-        <v>60.072000000000003</v>
+        <v>125.5</v>
       </c>
       <c r="D4">
-        <v>62.216999999999999</v>
+        <v>127.9</v>
       </c>
       <c r="E4">
-        <v>65.712000000000003</v>
+        <v>128.80000000000001</v>
       </c>
       <c r="F4">
-        <v>71.085999999999999</v>
+        <v>126.9</v>
       </c>
       <c r="G4">
-        <v>69.872</v>
+        <v>132</v>
       </c>
       <c r="H4">
-        <v>73.671000000000006</v>
+        <v>137.30000000000001</v>
       </c>
       <c r="I4">
-        <v>86.387</v>
+        <v>138.69999999999999</v>
       </c>
       <c r="J4">
-        <v>80.802000000000007</v>
+        <v>134.69999999999999</v>
       </c>
       <c r="K4">
-        <v>87.573999999999998</v>
+        <v>131.80000000000001</v>
       </c>
       <c r="L4">
-        <v>93.197000000000003</v>
+        <v>131.1</v>
       </c>
       <c r="M4">
-        <v>69.45</v>
+        <v>131.5</v>
       </c>
     </row>
   </sheetData>
@@ -606,6 +610,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D25CF0B9B9713944843C6634AD94B5CD" ma:contentTypeVersion="4" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="6fc06c35c9fb9ff8495a9005fb1aa923">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f4a0f2c8-0374-43bc-b7f6-d31395797ed2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ffa17790aa560c96c4a002fed6eed5a2" ns3:_="">
     <xsd:import namespace="f4a0f2c8-0374-43bc-b7f6-d31395797ed2"/>
@@ -749,15 +762,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -765,6 +769,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9BA2348-B4A9-433B-8E09-86B1A484E3C9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C64B52EA-6A09-4710-A973-6D7843483BB8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -782,14 +794,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9BA2348-B4A9-433B-8E09-86B1A484E3C9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADEAF920-3273-4C85-B8A9-2A3E9F7C5CAA}">
   <ds:schemaRefs/>
